--- a/冒险者角色档案.xlsx
+++ b/冒险者角色档案.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="153">
   <si>
     <t>基础信息</t>
   </si>
@@ -471,13 +471,22 @@
     <t>二阶天赋树（5）</t>
   </si>
   <si>
+    <t>三阶天赋树（5）</t>
+  </si>
+  <si>
+    <t>四阶天赋树（5）</t>
+  </si>
+  <si>
+    <t>五阶天赋树（5）</t>
+  </si>
+  <si>
+    <t>六阶天赋树（5）</t>
+  </si>
+  <si>
+    <t>七阶天赋树（5）</t>
+  </si>
+  <si>
     <t>子职业（）</t>
-  </si>
-  <si>
-    <t>三阶天赋树（5）</t>
-  </si>
-  <si>
-    <t>四阶天赋树（5）</t>
   </si>
 </sst>
 </file>
@@ -2122,7 +2131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:X147"/>
+  <dimension ref="B2:X209"/>
   <sheetFormatPr defaultColWidth="10.775" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.275" style="1" customWidth="1"/>
@@ -4777,6 +4786,18 @@
       <c r="S131" s="83"/>
     </row>
     <row r="132" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B132" s="15"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="63"/>
+      <c r="E132" s="63"/>
+      <c r="F132" s="60"/>
+      <c r="G132" s="61"/>
+      <c r="H132" s="63"/>
+      <c r="I132" s="63"/>
+      <c r="J132" s="60"/>
+      <c r="K132" s="84"/>
+      <c r="L132" s="84"/>
+      <c r="M132" s="61"/>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
       <c r="Q132" s="15"/>
@@ -4784,20 +4805,18 @@
       <c r="S132" s="83"/>
     </row>
     <row r="133" s="1" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B133" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
-      <c r="K133" s="7"/>
-      <c r="L133" s="7"/>
-      <c r="M133" s="8"/>
+      <c r="B133" s="15"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="63"/>
+      <c r="E133" s="63"/>
+      <c r="F133" s="60"/>
+      <c r="G133" s="61"/>
+      <c r="H133" s="63"/>
+      <c r="I133" s="63"/>
+      <c r="J133" s="60"/>
+      <c r="K133" s="84"/>
+      <c r="L133" s="84"/>
+      <c r="M133" s="61"/>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="15"/>
@@ -4805,32 +4824,18 @@
       <c r="S133" s="83"/>
     </row>
     <row r="134" s="1" customFormat="1" customHeight="1" spans="2:19">
-      <c r="B134" s="78" t="s">
-        <v>141</v>
-      </c>
-      <c r="C134" s="79"/>
-      <c r="D134" s="80" t="s">
-        <v>142</v>
-      </c>
-      <c r="E134" s="80" t="s">
-        <v>143</v>
-      </c>
-      <c r="F134" s="81" t="s">
-        <v>144</v>
-      </c>
-      <c r="G134" s="82"/>
-      <c r="H134" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="I134" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="8"/>
+      <c r="B134" s="15"/>
+      <c r="C134" s="16"/>
+      <c r="D134" s="63"/>
+      <c r="E134" s="63"/>
+      <c r="F134" s="60"/>
+      <c r="G134" s="61"/>
+      <c r="H134" s="63"/>
+      <c r="I134" s="63"/>
+      <c r="J134" s="60"/>
+      <c r="K134" s="84"/>
+      <c r="L134" s="84"/>
+      <c r="M134" s="61"/>
     </row>
     <row r="135" s="1" customFormat="1" customHeight="1" spans="2:19">
       <c r="B135" s="15"/>
@@ -4846,7 +4851,7 @@
       <c r="L135" s="84"/>
       <c r="M135" s="61"/>
       <c r="O135" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P135" s="7"/>
       <c r="Q135" s="7"/>
@@ -4892,6 +4897,18 @@
       <c r="S137" s="83"/>
     </row>
     <row r="138" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B138" s="15"/>
+      <c r="C138" s="16"/>
+      <c r="D138" s="63"/>
+      <c r="E138" s="63"/>
+      <c r="F138" s="60"/>
+      <c r="G138" s="61"/>
+      <c r="H138" s="63"/>
+      <c r="I138" s="63"/>
+      <c r="J138" s="60"/>
+      <c r="K138" s="84"/>
+      <c r="L138" s="84"/>
+      <c r="M138" s="61"/>
       <c r="O138" s="15"/>
       <c r="P138" s="16"/>
       <c r="Q138" s="15"/>
@@ -4899,6 +4916,18 @@
       <c r="S138" s="83"/>
     </row>
     <row r="139" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B139" s="15"/>
+      <c r="C139" s="16"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="60"/>
+      <c r="G139" s="61"/>
+      <c r="H139" s="63"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="60"/>
+      <c r="K139" s="84"/>
+      <c r="L139" s="84"/>
+      <c r="M139" s="61"/>
       <c r="O139" s="15"/>
       <c r="P139" s="16"/>
       <c r="Q139" s="15"/>
@@ -4906,15 +4935,53 @@
       <c r="S139" s="83"/>
     </row>
     <row r="140" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B140" s="15"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="63"/>
+      <c r="E140" s="63"/>
+      <c r="F140" s="60"/>
+      <c r="G140" s="61"/>
+      <c r="H140" s="63"/>
+      <c r="I140" s="63"/>
+      <c r="J140" s="60"/>
+      <c r="K140" s="84"/>
+      <c r="L140" s="84"/>
+      <c r="M140" s="61"/>
       <c r="O140" s="15"/>
       <c r="P140" s="16"/>
       <c r="Q140" s="15"/>
       <c r="R140" s="16"/>
       <c r="S140" s="83"/>
     </row>
+    <row r="141" customHeight="1" spans="2:19">
+      <c r="B141" s="15"/>
+      <c r="C141" s="16"/>
+      <c r="D141" s="63"/>
+      <c r="E141" s="63"/>
+      <c r="F141" s="60"/>
+      <c r="G141" s="61"/>
+      <c r="H141" s="63"/>
+      <c r="I141" s="63"/>
+      <c r="J141" s="60"/>
+      <c r="K141" s="84"/>
+      <c r="L141" s="84"/>
+      <c r="M141" s="61"/>
+    </row>
     <row r="142" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B142" s="15"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="63"/>
+      <c r="E142" s="63"/>
+      <c r="F142" s="60"/>
+      <c r="G142" s="61"/>
+      <c r="H142" s="63"/>
+      <c r="I142" s="63"/>
+      <c r="J142" s="60"/>
+      <c r="K142" s="84"/>
+      <c r="L142" s="84"/>
+      <c r="M142" s="61"/>
       <c r="O142" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P142" s="7"/>
       <c r="Q142" s="7"/>
@@ -4922,6 +4989,18 @@
       <c r="S142" s="8"/>
     </row>
     <row r="143" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B143" s="15"/>
+      <c r="C143" s="16"/>
+      <c r="D143" s="63"/>
+      <c r="E143" s="63"/>
+      <c r="F143" s="60"/>
+      <c r="G143" s="61"/>
+      <c r="H143" s="63"/>
+      <c r="I143" s="63"/>
+      <c r="J143" s="60"/>
+      <c r="K143" s="84"/>
+      <c r="L143" s="84"/>
+      <c r="M143" s="61"/>
       <c r="O143" s="15"/>
       <c r="P143" s="16"/>
       <c r="Q143" s="15"/>
@@ -4929,35 +5008,1027 @@
       <c r="S143" s="83"/>
     </row>
     <row r="144" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B144" s="15"/>
+      <c r="C144" s="16"/>
+      <c r="D144" s="63"/>
+      <c r="E144" s="63"/>
+      <c r="F144" s="60"/>
+      <c r="G144" s="61"/>
+      <c r="H144" s="63"/>
+      <c r="I144" s="63"/>
+      <c r="J144" s="60"/>
+      <c r="K144" s="84"/>
+      <c r="L144" s="84"/>
+      <c r="M144" s="61"/>
       <c r="O144" s="15"/>
       <c r="P144" s="16"/>
       <c r="Q144" s="15"/>
       <c r="R144" s="16"/>
       <c r="S144" s="83"/>
     </row>
-    <row r="145" s="1" customFormat="1" customHeight="1" spans="15:19">
+    <row r="145" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B145" s="15"/>
+      <c r="C145" s="16"/>
+      <c r="D145" s="63"/>
+      <c r="E145" s="63"/>
+      <c r="F145" s="60"/>
+      <c r="G145" s="61"/>
+      <c r="H145" s="63"/>
+      <c r="I145" s="63"/>
+      <c r="J145" s="60"/>
+      <c r="K145" s="84"/>
+      <c r="L145" s="84"/>
+      <c r="M145" s="61"/>
       <c r="O145" s="15"/>
       <c r="P145" s="16"/>
       <c r="Q145" s="15"/>
       <c r="R145" s="16"/>
       <c r="S145" s="83"/>
     </row>
-    <row r="146" s="1" customFormat="1" customHeight="1" spans="15:19">
+    <row r="146" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B146" s="15"/>
+      <c r="C146" s="16"/>
+      <c r="D146" s="63"/>
+      <c r="E146" s="63"/>
+      <c r="F146" s="60"/>
+      <c r="G146" s="61"/>
+      <c r="H146" s="63"/>
+      <c r="I146" s="63"/>
+      <c r="J146" s="60"/>
+      <c r="K146" s="84"/>
+      <c r="L146" s="84"/>
+      <c r="M146" s="61"/>
       <c r="O146" s="15"/>
       <c r="P146" s="16"/>
       <c r="Q146" s="15"/>
       <c r="R146" s="16"/>
       <c r="S146" s="83"/>
     </row>
-    <row r="147" s="1" customFormat="1" customHeight="1" spans="15:19">
+    <row r="147" s="1" customFormat="1" customHeight="1" spans="2:19">
+      <c r="B147" s="15"/>
+      <c r="C147" s="16"/>
+      <c r="D147" s="63"/>
+      <c r="E147" s="63"/>
+      <c r="F147" s="60"/>
+      <c r="G147" s="61"/>
+      <c r="H147" s="63"/>
+      <c r="I147" s="63"/>
+      <c r="J147" s="60"/>
+      <c r="K147" s="84"/>
+      <c r="L147" s="84"/>
+      <c r="M147" s="61"/>
       <c r="O147" s="15"/>
       <c r="P147" s="16"/>
       <c r="Q147" s="15"/>
       <c r="R147" s="16"/>
       <c r="S147" s="83"/>
     </row>
+    <row r="148" customHeight="1" spans="2:19">
+      <c r="B148" s="15"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="63"/>
+      <c r="E148" s="63"/>
+      <c r="F148" s="60"/>
+      <c r="G148" s="61"/>
+      <c r="H148" s="63"/>
+      <c r="I148" s="63"/>
+      <c r="J148" s="60"/>
+      <c r="K148" s="84"/>
+      <c r="L148" s="84"/>
+      <c r="M148" s="61"/>
+    </row>
+    <row r="149" customHeight="1" spans="2:19">
+      <c r="B149" s="15"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="63"/>
+      <c r="E149" s="63"/>
+      <c r="F149" s="60"/>
+      <c r="G149" s="61"/>
+      <c r="H149" s="63"/>
+      <c r="I149" s="63"/>
+      <c r="J149" s="60"/>
+      <c r="K149" s="84"/>
+      <c r="L149" s="84"/>
+      <c r="M149" s="61"/>
+      <c r="O149" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P149" s="7"/>
+      <c r="Q149" s="7"/>
+      <c r="R149" s="7"/>
+      <c r="S149" s="8"/>
+    </row>
+    <row r="150" customHeight="1" spans="2:19">
+      <c r="B150" s="15"/>
+      <c r="C150" s="16"/>
+      <c r="D150" s="63"/>
+      <c r="E150" s="63"/>
+      <c r="F150" s="60"/>
+      <c r="G150" s="61"/>
+      <c r="H150" s="63"/>
+      <c r="I150" s="63"/>
+      <c r="J150" s="60"/>
+      <c r="K150" s="84"/>
+      <c r="L150" s="84"/>
+      <c r="M150" s="61"/>
+      <c r="O150" s="15"/>
+      <c r="P150" s="16"/>
+      <c r="Q150" s="15"/>
+      <c r="R150" s="16"/>
+      <c r="S150" s="83"/>
+    </row>
+    <row r="151" customHeight="1" spans="2:19">
+      <c r="B151" s="15"/>
+      <c r="C151" s="16"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="60"/>
+      <c r="G151" s="61"/>
+      <c r="H151" s="63"/>
+      <c r="I151" s="63"/>
+      <c r="J151" s="60"/>
+      <c r="K151" s="84"/>
+      <c r="L151" s="84"/>
+      <c r="M151" s="61"/>
+      <c r="O151" s="15"/>
+      <c r="P151" s="16"/>
+      <c r="Q151" s="15"/>
+      <c r="R151" s="16"/>
+      <c r="S151" s="83"/>
+    </row>
+    <row r="152" customHeight="1" spans="2:19">
+      <c r="B152" s="15"/>
+      <c r="C152" s="16"/>
+      <c r="D152" s="63"/>
+      <c r="E152" s="63"/>
+      <c r="F152" s="60"/>
+      <c r="G152" s="61"/>
+      <c r="H152" s="63"/>
+      <c r="I152" s="63"/>
+      <c r="J152" s="60"/>
+      <c r="K152" s="84"/>
+      <c r="L152" s="84"/>
+      <c r="M152" s="61"/>
+      <c r="O152" s="15"/>
+      <c r="P152" s="16"/>
+      <c r="Q152" s="15"/>
+      <c r="R152" s="16"/>
+      <c r="S152" s="83"/>
+    </row>
+    <row r="153" customHeight="1" spans="2:19">
+      <c r="B153" s="15"/>
+      <c r="C153" s="16"/>
+      <c r="D153" s="63"/>
+      <c r="E153" s="63"/>
+      <c r="F153" s="60"/>
+      <c r="G153" s="61"/>
+      <c r="H153" s="63"/>
+      <c r="I153" s="63"/>
+      <c r="J153" s="60"/>
+      <c r="K153" s="84"/>
+      <c r="L153" s="84"/>
+      <c r="M153" s="61"/>
+      <c r="O153" s="15"/>
+      <c r="P153" s="16"/>
+      <c r="Q153" s="15"/>
+      <c r="R153" s="16"/>
+      <c r="S153" s="83"/>
+    </row>
+    <row r="154" customHeight="1" spans="2:19">
+      <c r="B154" s="15"/>
+      <c r="C154" s="16"/>
+      <c r="D154" s="63"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="60"/>
+      <c r="G154" s="61"/>
+      <c r="H154" s="63"/>
+      <c r="I154" s="63"/>
+      <c r="J154" s="60"/>
+      <c r="K154" s="84"/>
+      <c r="L154" s="84"/>
+      <c r="M154" s="61"/>
+      <c r="O154" s="15"/>
+      <c r="P154" s="16"/>
+      <c r="Q154" s="15"/>
+      <c r="R154" s="16"/>
+      <c r="S154" s="83"/>
+    </row>
+    <row r="155" customHeight="1" spans="2:19">
+      <c r="B155" s="15"/>
+      <c r="C155" s="16"/>
+      <c r="D155" s="63"/>
+      <c r="E155" s="63"/>
+      <c r="F155" s="60"/>
+      <c r="G155" s="61"/>
+      <c r="H155" s="63"/>
+      <c r="I155" s="63"/>
+      <c r="J155" s="60"/>
+      <c r="K155" s="84"/>
+      <c r="L155" s="84"/>
+      <c r="M155" s="61"/>
+    </row>
+    <row r="156" customHeight="1" spans="2:19">
+      <c r="B156" s="15"/>
+      <c r="C156" s="16"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="60"/>
+      <c r="G156" s="61"/>
+      <c r="H156" s="63"/>
+      <c r="I156" s="63"/>
+      <c r="J156" s="60"/>
+      <c r="K156" s="84"/>
+      <c r="L156" s="84"/>
+      <c r="M156" s="61"/>
+      <c r="O156" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="P156" s="7"/>
+      <c r="Q156" s="7"/>
+      <c r="R156" s="7"/>
+      <c r="S156" s="8"/>
+    </row>
+    <row r="157" customHeight="1" spans="2:19">
+      <c r="B157" s="15"/>
+      <c r="C157" s="16"/>
+      <c r="D157" s="63"/>
+      <c r="E157" s="63"/>
+      <c r="F157" s="60"/>
+      <c r="G157" s="61"/>
+      <c r="H157" s="63"/>
+      <c r="I157" s="63"/>
+      <c r="J157" s="60"/>
+      <c r="K157" s="84"/>
+      <c r="L157" s="84"/>
+      <c r="M157" s="61"/>
+      <c r="O157" s="15"/>
+      <c r="P157" s="16"/>
+      <c r="Q157" s="15"/>
+      <c r="R157" s="16"/>
+      <c r="S157" s="83"/>
+    </row>
+    <row r="158" customHeight="1" spans="2:19">
+      <c r="B158" s="15"/>
+      <c r="C158" s="16"/>
+      <c r="D158" s="63"/>
+      <c r="E158" s="63"/>
+      <c r="F158" s="60"/>
+      <c r="G158" s="61"/>
+      <c r="H158" s="63"/>
+      <c r="I158" s="63"/>
+      <c r="J158" s="60"/>
+      <c r="K158" s="84"/>
+      <c r="L158" s="84"/>
+      <c r="M158" s="61"/>
+      <c r="O158" s="15"/>
+      <c r="P158" s="16"/>
+      <c r="Q158" s="15"/>
+      <c r="R158" s="16"/>
+      <c r="S158" s="83"/>
+    </row>
+    <row r="159" customHeight="1" spans="2:19">
+      <c r="B159" s="15"/>
+      <c r="C159" s="16"/>
+      <c r="D159" s="63"/>
+      <c r="E159" s="63"/>
+      <c r="F159" s="60"/>
+      <c r="G159" s="61"/>
+      <c r="H159" s="63"/>
+      <c r="I159" s="63"/>
+      <c r="J159" s="60"/>
+      <c r="K159" s="84"/>
+      <c r="L159" s="84"/>
+      <c r="M159" s="61"/>
+      <c r="O159" s="15"/>
+      <c r="P159" s="16"/>
+      <c r="Q159" s="15"/>
+      <c r="R159" s="16"/>
+      <c r="S159" s="83"/>
+    </row>
+    <row r="160" customHeight="1" spans="2:19">
+      <c r="B160" s="15"/>
+      <c r="C160" s="16"/>
+      <c r="D160" s="63"/>
+      <c r="E160" s="63"/>
+      <c r="F160" s="60"/>
+      <c r="G160" s="61"/>
+      <c r="H160" s="63"/>
+      <c r="I160" s="63"/>
+      <c r="J160" s="60"/>
+      <c r="K160" s="84"/>
+      <c r="L160" s="84"/>
+      <c r="M160" s="61"/>
+      <c r="O160" s="15"/>
+      <c r="P160" s="16"/>
+      <c r="Q160" s="15"/>
+      <c r="R160" s="16"/>
+      <c r="S160" s="83"/>
+    </row>
+    <row r="161" customHeight="1" spans="2:19">
+      <c r="B161" s="15"/>
+      <c r="C161" s="16"/>
+      <c r="D161" s="63"/>
+      <c r="E161" s="63"/>
+      <c r="F161" s="60"/>
+      <c r="G161" s="61"/>
+      <c r="H161" s="63"/>
+      <c r="I161" s="63"/>
+      <c r="J161" s="60"/>
+      <c r="K161" s="84"/>
+      <c r="L161" s="84"/>
+      <c r="M161" s="61"/>
+      <c r="O161" s="15"/>
+      <c r="P161" s="16"/>
+      <c r="Q161" s="15"/>
+      <c r="R161" s="16"/>
+      <c r="S161" s="83"/>
+    </row>
+    <row r="162" customHeight="1" spans="2:19">
+      <c r="B162" s="15"/>
+      <c r="C162" s="16"/>
+      <c r="D162" s="63"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="60"/>
+      <c r="G162" s="61"/>
+      <c r="H162" s="63"/>
+      <c r="I162" s="63"/>
+      <c r="J162" s="60"/>
+      <c r="K162" s="84"/>
+      <c r="L162" s="84"/>
+      <c r="M162" s="61"/>
+    </row>
+    <row r="163" customHeight="1" spans="2:19">
+      <c r="O163" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="P163" s="7"/>
+      <c r="Q163" s="7"/>
+      <c r="R163" s="7"/>
+      <c r="S163" s="8"/>
+    </row>
+    <row r="164" customHeight="1" spans="2:19">
+      <c r="O164" s="15"/>
+      <c r="P164" s="16"/>
+      <c r="Q164" s="15"/>
+      <c r="R164" s="16"/>
+      <c r="S164" s="83"/>
+    </row>
+    <row r="165" customHeight="1" spans="2:19">
+      <c r="O165" s="15"/>
+      <c r="P165" s="16"/>
+      <c r="Q165" s="15"/>
+      <c r="R165" s="16"/>
+      <c r="S165" s="83"/>
+    </row>
+    <row r="166" customHeight="1" spans="2:19">
+      <c r="B166" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
+      <c r="G166" s="7"/>
+      <c r="H166" s="7"/>
+      <c r="I166" s="7"/>
+      <c r="J166" s="7"/>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
+      <c r="M166" s="8"/>
+      <c r="O166" s="15"/>
+      <c r="P166" s="16"/>
+      <c r="Q166" s="15"/>
+      <c r="R166" s="16"/>
+      <c r="S166" s="83"/>
+    </row>
+    <row r="167" customHeight="1" spans="2:19">
+      <c r="B167" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="C167" s="79"/>
+      <c r="D167" s="80" t="s">
+        <v>142</v>
+      </c>
+      <c r="E167" s="80" t="s">
+        <v>143</v>
+      </c>
+      <c r="F167" s="81" t="s">
+        <v>144</v>
+      </c>
+      <c r="G167" s="82"/>
+      <c r="H167" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I167" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K167" s="7"/>
+      <c r="L167" s="7"/>
+      <c r="M167" s="8"/>
+      <c r="O167" s="15"/>
+      <c r="P167" s="16"/>
+      <c r="Q167" s="15"/>
+      <c r="R167" s="16"/>
+      <c r="S167" s="83"/>
+    </row>
+    <row r="168" customHeight="1" spans="2:19">
+      <c r="B168" s="15"/>
+      <c r="C168" s="16"/>
+      <c r="D168" s="63"/>
+      <c r="E168" s="63"/>
+      <c r="F168" s="60"/>
+      <c r="G168" s="61"/>
+      <c r="H168" s="63"/>
+      <c r="I168" s="63"/>
+      <c r="J168" s="60"/>
+      <c r="K168" s="84"/>
+      <c r="L168" s="84"/>
+      <c r="M168" s="61"/>
+      <c r="O168" s="15"/>
+      <c r="P168" s="16"/>
+      <c r="Q168" s="15"/>
+      <c r="R168" s="16"/>
+      <c r="S168" s="83"/>
+    </row>
+    <row r="169" customHeight="1" spans="2:19">
+      <c r="B169" s="15"/>
+      <c r="C169" s="16"/>
+      <c r="D169" s="63"/>
+      <c r="E169" s="63"/>
+      <c r="F169" s="60"/>
+      <c r="G169" s="61"/>
+      <c r="H169" s="63"/>
+      <c r="I169" s="63"/>
+      <c r="J169" s="60"/>
+      <c r="K169" s="84"/>
+      <c r="L169" s="84"/>
+      <c r="M169" s="61"/>
+    </row>
+    <row r="170" customHeight="1" spans="2:19">
+      <c r="B170" s="15"/>
+      <c r="C170" s="16"/>
+      <c r="D170" s="63"/>
+      <c r="E170" s="63"/>
+      <c r="F170" s="60"/>
+      <c r="G170" s="61"/>
+      <c r="H170" s="63"/>
+      <c r="I170" s="63"/>
+      <c r="J170" s="60"/>
+      <c r="K170" s="84"/>
+      <c r="L170" s="84"/>
+      <c r="M170" s="61"/>
+    </row>
+    <row r="171" customHeight="1" spans="2:19">
+      <c r="B171" s="15"/>
+      <c r="C171" s="16"/>
+      <c r="D171" s="63"/>
+      <c r="E171" s="63"/>
+      <c r="F171" s="60"/>
+      <c r="G171" s="61"/>
+      <c r="H171" s="63"/>
+      <c r="I171" s="63"/>
+      <c r="J171" s="60"/>
+      <c r="K171" s="84"/>
+      <c r="L171" s="84"/>
+      <c r="M171" s="61"/>
+    </row>
+    <row r="172" customHeight="1" spans="2:19">
+      <c r="B172" s="15"/>
+      <c r="C172" s="16"/>
+      <c r="D172" s="63"/>
+      <c r="E172" s="63"/>
+      <c r="F172" s="60"/>
+      <c r="G172" s="61"/>
+      <c r="H172" s="63"/>
+      <c r="I172" s="63"/>
+      <c r="J172" s="60"/>
+      <c r="K172" s="84"/>
+      <c r="L172" s="84"/>
+      <c r="M172" s="61"/>
+    </row>
+    <row r="173" customHeight="1" spans="2:19">
+      <c r="B173" s="15"/>
+      <c r="C173" s="16"/>
+      <c r="D173" s="63"/>
+      <c r="E173" s="63"/>
+      <c r="F173" s="60"/>
+      <c r="G173" s="61"/>
+      <c r="H173" s="63"/>
+      <c r="I173" s="63"/>
+      <c r="J173" s="60"/>
+      <c r="K173" s="84"/>
+      <c r="L173" s="84"/>
+      <c r="M173" s="61"/>
+    </row>
+    <row r="174" customHeight="1" spans="2:19">
+      <c r="B174" s="15"/>
+      <c r="C174" s="16"/>
+      <c r="D174" s="63"/>
+      <c r="E174" s="63"/>
+      <c r="F174" s="60"/>
+      <c r="G174" s="61"/>
+      <c r="H174" s="63"/>
+      <c r="I174" s="63"/>
+      <c r="J174" s="60"/>
+      <c r="K174" s="84"/>
+      <c r="L174" s="84"/>
+      <c r="M174" s="61"/>
+    </row>
+    <row r="175" customHeight="1" spans="2:19">
+      <c r="B175" s="15"/>
+      <c r="C175" s="16"/>
+      <c r="D175" s="63"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="60"/>
+      <c r="G175" s="61"/>
+      <c r="H175" s="63"/>
+      <c r="I175" s="63"/>
+      <c r="J175" s="60"/>
+      <c r="K175" s="84"/>
+      <c r="L175" s="84"/>
+      <c r="M175" s="61"/>
+    </row>
+    <row r="176" customHeight="1" spans="2:19">
+      <c r="B176" s="15"/>
+      <c r="C176" s="16"/>
+      <c r="D176" s="63"/>
+      <c r="E176" s="63"/>
+      <c r="F176" s="60"/>
+      <c r="G176" s="61"/>
+      <c r="H176" s="63"/>
+      <c r="I176" s="63"/>
+      <c r="J176" s="60"/>
+      <c r="K176" s="84"/>
+      <c r="L176" s="84"/>
+      <c r="M176" s="61"/>
+    </row>
+    <row r="177" customHeight="1" spans="2:13">
+      <c r="B177" s="15"/>
+      <c r="C177" s="16"/>
+      <c r="D177" s="63"/>
+      <c r="E177" s="63"/>
+      <c r="F177" s="60"/>
+      <c r="G177" s="61"/>
+      <c r="H177" s="63"/>
+      <c r="I177" s="63"/>
+      <c r="J177" s="60"/>
+      <c r="K177" s="84"/>
+      <c r="L177" s="84"/>
+      <c r="M177" s="61"/>
+    </row>
+    <row r="178" customHeight="1" spans="2:13">
+      <c r="B178" s="15"/>
+      <c r="C178" s="16"/>
+      <c r="D178" s="63"/>
+      <c r="E178" s="63"/>
+      <c r="F178" s="60"/>
+      <c r="G178" s="61"/>
+      <c r="H178" s="63"/>
+      <c r="I178" s="63"/>
+      <c r="J178" s="60"/>
+      <c r="K178" s="84"/>
+      <c r="L178" s="84"/>
+      <c r="M178" s="61"/>
+    </row>
+    <row r="179" customHeight="1" spans="2:13">
+      <c r="B179" s="15"/>
+      <c r="C179" s="16"/>
+      <c r="D179" s="63"/>
+      <c r="E179" s="63"/>
+      <c r="F179" s="60"/>
+      <c r="G179" s="61"/>
+      <c r="H179" s="63"/>
+      <c r="I179" s="63"/>
+      <c r="J179" s="60"/>
+      <c r="K179" s="84"/>
+      <c r="L179" s="84"/>
+      <c r="M179" s="61"/>
+    </row>
+    <row r="180" customHeight="1" spans="2:13">
+      <c r="B180" s="15"/>
+      <c r="C180" s="16"/>
+      <c r="D180" s="63"/>
+      <c r="E180" s="63"/>
+      <c r="F180" s="60"/>
+      <c r="G180" s="61"/>
+      <c r="H180" s="63"/>
+      <c r="I180" s="63"/>
+      <c r="J180" s="60"/>
+      <c r="K180" s="84"/>
+      <c r="L180" s="84"/>
+      <c r="M180" s="61"/>
+    </row>
+    <row r="181" customHeight="1" spans="2:13">
+      <c r="B181" s="15"/>
+      <c r="C181" s="16"/>
+      <c r="D181" s="63"/>
+      <c r="E181" s="63"/>
+      <c r="F181" s="60"/>
+      <c r="G181" s="61"/>
+      <c r="H181" s="63"/>
+      <c r="I181" s="63"/>
+      <c r="J181" s="60"/>
+      <c r="K181" s="84"/>
+      <c r="L181" s="84"/>
+      <c r="M181" s="61"/>
+    </row>
+    <row r="182" customHeight="1" spans="2:13">
+      <c r="B182" s="15"/>
+      <c r="C182" s="16"/>
+      <c r="D182" s="63"/>
+      <c r="E182" s="63"/>
+      <c r="F182" s="60"/>
+      <c r="G182" s="61"/>
+      <c r="H182" s="63"/>
+      <c r="I182" s="63"/>
+      <c r="J182" s="60"/>
+      <c r="K182" s="84"/>
+      <c r="L182" s="84"/>
+      <c r="M182" s="61"/>
+    </row>
+    <row r="183" customHeight="1" spans="2:13">
+      <c r="B183" s="15"/>
+      <c r="C183" s="16"/>
+      <c r="D183" s="63"/>
+      <c r="E183" s="63"/>
+      <c r="F183" s="60"/>
+      <c r="G183" s="61"/>
+      <c r="H183" s="63"/>
+      <c r="I183" s="63"/>
+      <c r="J183" s="60"/>
+      <c r="K183" s="84"/>
+      <c r="L183" s="84"/>
+      <c r="M183" s="61"/>
+    </row>
+    <row r="184" customHeight="1" spans="2:13">
+      <c r="B184" s="15"/>
+      <c r="C184" s="16"/>
+      <c r="D184" s="63"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="60"/>
+      <c r="G184" s="61"/>
+      <c r="H184" s="63"/>
+      <c r="I184" s="63"/>
+      <c r="J184" s="60"/>
+      <c r="K184" s="84"/>
+      <c r="L184" s="84"/>
+      <c r="M184" s="61"/>
+    </row>
+    <row r="185" customHeight="1" spans="2:13">
+      <c r="B185" s="15"/>
+      <c r="C185" s="16"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="60"/>
+      <c r="G185" s="61"/>
+      <c r="H185" s="63"/>
+      <c r="I185" s="63"/>
+      <c r="J185" s="60"/>
+      <c r="K185" s="84"/>
+      <c r="L185" s="84"/>
+      <c r="M185" s="61"/>
+    </row>
+    <row r="186" customHeight="1" spans="2:13">
+      <c r="B186" s="15"/>
+      <c r="C186" s="16"/>
+      <c r="D186" s="63"/>
+      <c r="E186" s="63"/>
+      <c r="F186" s="60"/>
+      <c r="G186" s="61"/>
+      <c r="H186" s="63"/>
+      <c r="I186" s="63"/>
+      <c r="J186" s="60"/>
+      <c r="K186" s="84"/>
+      <c r="L186" s="84"/>
+      <c r="M186" s="61"/>
+    </row>
+    <row r="187" customHeight="1" spans="2:13">
+      <c r="B187" s="15"/>
+      <c r="C187" s="16"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="60"/>
+      <c r="G187" s="61"/>
+      <c r="H187" s="63"/>
+      <c r="I187" s="63"/>
+      <c r="J187" s="60"/>
+      <c r="K187" s="84"/>
+      <c r="L187" s="84"/>
+      <c r="M187" s="61"/>
+    </row>
+    <row r="188" customHeight="1" spans="2:13">
+      <c r="B188" s="15"/>
+      <c r="C188" s="16"/>
+      <c r="D188" s="63"/>
+      <c r="E188" s="63"/>
+      <c r="F188" s="60"/>
+      <c r="G188" s="61"/>
+      <c r="H188" s="63"/>
+      <c r="I188" s="63"/>
+      <c r="J188" s="60"/>
+      <c r="K188" s="84"/>
+      <c r="L188" s="84"/>
+      <c r="M188" s="61"/>
+    </row>
+    <row r="189" customHeight="1" spans="2:13">
+      <c r="B189" s="15"/>
+      <c r="C189" s="16"/>
+      <c r="D189" s="63"/>
+      <c r="E189" s="63"/>
+      <c r="F189" s="60"/>
+      <c r="G189" s="61"/>
+      <c r="H189" s="63"/>
+      <c r="I189" s="63"/>
+      <c r="J189" s="60"/>
+      <c r="K189" s="84"/>
+      <c r="L189" s="84"/>
+      <c r="M189" s="61"/>
+    </row>
+    <row r="190" customHeight="1" spans="2:13">
+      <c r="B190" s="15"/>
+      <c r="C190" s="16"/>
+      <c r="D190" s="63"/>
+      <c r="E190" s="63"/>
+      <c r="F190" s="60"/>
+      <c r="G190" s="61"/>
+      <c r="H190" s="63"/>
+      <c r="I190" s="63"/>
+      <c r="J190" s="60"/>
+      <c r="K190" s="84"/>
+      <c r="L190" s="84"/>
+      <c r="M190" s="61"/>
+    </row>
+    <row r="191" customHeight="1" spans="2:13">
+      <c r="B191" s="15"/>
+      <c r="C191" s="16"/>
+      <c r="D191" s="63"/>
+      <c r="E191" s="63"/>
+      <c r="F191" s="60"/>
+      <c r="G191" s="61"/>
+      <c r="H191" s="63"/>
+      <c r="I191" s="63"/>
+      <c r="J191" s="60"/>
+      <c r="K191" s="84"/>
+      <c r="L191" s="84"/>
+      <c r="M191" s="61"/>
+    </row>
+    <row r="192" customHeight="1" spans="2:13">
+      <c r="B192" s="15"/>
+      <c r="C192" s="16"/>
+      <c r="D192" s="63"/>
+      <c r="E192" s="63"/>
+      <c r="F192" s="60"/>
+      <c r="G192" s="61"/>
+      <c r="H192" s="63"/>
+      <c r="I192" s="63"/>
+      <c r="J192" s="60"/>
+      <c r="K192" s="84"/>
+      <c r="L192" s="84"/>
+      <c r="M192" s="61"/>
+    </row>
+    <row r="193" customHeight="1" spans="2:13">
+      <c r="B193" s="15"/>
+      <c r="C193" s="16"/>
+      <c r="D193" s="63"/>
+      <c r="E193" s="63"/>
+      <c r="F193" s="60"/>
+      <c r="G193" s="61"/>
+      <c r="H193" s="63"/>
+      <c r="I193" s="63"/>
+      <c r="J193" s="60"/>
+      <c r="K193" s="84"/>
+      <c r="L193" s="84"/>
+      <c r="M193" s="61"/>
+    </row>
+    <row r="194" customHeight="1" spans="2:13">
+      <c r="B194" s="15"/>
+      <c r="C194" s="16"/>
+      <c r="D194" s="63"/>
+      <c r="E194" s="63"/>
+      <c r="F194" s="60"/>
+      <c r="G194" s="61"/>
+      <c r="H194" s="63"/>
+      <c r="I194" s="63"/>
+      <c r="J194" s="60"/>
+      <c r="K194" s="84"/>
+      <c r="L194" s="84"/>
+      <c r="M194" s="61"/>
+    </row>
+    <row r="195" customHeight="1" spans="2:13">
+      <c r="B195" s="15"/>
+      <c r="C195" s="16"/>
+      <c r="D195" s="63"/>
+      <c r="E195" s="63"/>
+      <c r="F195" s="60"/>
+      <c r="G195" s="61"/>
+      <c r="H195" s="63"/>
+      <c r="I195" s="63"/>
+      <c r="J195" s="60"/>
+      <c r="K195" s="84"/>
+      <c r="L195" s="84"/>
+      <c r="M195" s="61"/>
+    </row>
+    <row r="196" customHeight="1" spans="2:13">
+      <c r="B196" s="15"/>
+      <c r="C196" s="16"/>
+      <c r="D196" s="63"/>
+      <c r="E196" s="63"/>
+      <c r="F196" s="60"/>
+      <c r="G196" s="61"/>
+      <c r="H196" s="63"/>
+      <c r="I196" s="63"/>
+      <c r="J196" s="60"/>
+      <c r="K196" s="84"/>
+      <c r="L196" s="84"/>
+      <c r="M196" s="61"/>
+    </row>
+    <row r="197" customHeight="1" spans="2:13">
+      <c r="B197" s="15"/>
+      <c r="C197" s="16"/>
+      <c r="D197" s="63"/>
+      <c r="E197" s="63"/>
+      <c r="F197" s="60"/>
+      <c r="G197" s="61"/>
+      <c r="H197" s="63"/>
+      <c r="I197" s="63"/>
+      <c r="J197" s="60"/>
+      <c r="K197" s="84"/>
+      <c r="L197" s="84"/>
+      <c r="M197" s="61"/>
+    </row>
+    <row r="198" customHeight="1" spans="2:13">
+      <c r="B198" s="15"/>
+      <c r="C198" s="16"/>
+      <c r="D198" s="63"/>
+      <c r="E198" s="63"/>
+      <c r="F198" s="60"/>
+      <c r="G198" s="61"/>
+      <c r="H198" s="63"/>
+      <c r="I198" s="63"/>
+      <c r="J198" s="60"/>
+      <c r="K198" s="84"/>
+      <c r="L198" s="84"/>
+      <c r="M198" s="61"/>
+    </row>
+    <row r="199" customHeight="1" spans="2:13">
+      <c r="B199" s="15"/>
+      <c r="C199" s="16"/>
+      <c r="D199" s="63"/>
+      <c r="E199" s="63"/>
+      <c r="F199" s="60"/>
+      <c r="G199" s="61"/>
+      <c r="H199" s="63"/>
+      <c r="I199" s="63"/>
+      <c r="J199" s="60"/>
+      <c r="K199" s="84"/>
+      <c r="L199" s="84"/>
+      <c r="M199" s="61"/>
+    </row>
+    <row r="200" customHeight="1" spans="2:13">
+      <c r="B200" s="15"/>
+      <c r="C200" s="16"/>
+      <c r="D200" s="63"/>
+      <c r="E200" s="63"/>
+      <c r="F200" s="60"/>
+      <c r="G200" s="61"/>
+      <c r="H200" s="63"/>
+      <c r="I200" s="63"/>
+      <c r="J200" s="60"/>
+      <c r="K200" s="84"/>
+      <c r="L200" s="84"/>
+      <c r="M200" s="61"/>
+    </row>
+    <row r="201" customHeight="1" spans="2:13">
+      <c r="B201" s="15"/>
+      <c r="C201" s="16"/>
+      <c r="D201" s="63"/>
+      <c r="E201" s="63"/>
+      <c r="F201" s="60"/>
+      <c r="G201" s="61"/>
+      <c r="H201" s="63"/>
+      <c r="I201" s="63"/>
+      <c r="J201" s="60"/>
+      <c r="K201" s="84"/>
+      <c r="L201" s="84"/>
+      <c r="M201" s="61"/>
+    </row>
+    <row r="202" customHeight="1" spans="2:13">
+      <c r="B202" s="15"/>
+      <c r="C202" s="16"/>
+      <c r="D202" s="63"/>
+      <c r="E202" s="63"/>
+      <c r="F202" s="60"/>
+      <c r="G202" s="61"/>
+      <c r="H202" s="63"/>
+      <c r="I202" s="63"/>
+      <c r="J202" s="60"/>
+      <c r="K202" s="84"/>
+      <c r="L202" s="84"/>
+      <c r="M202" s="61"/>
+    </row>
+    <row r="203" customHeight="1" spans="2:13">
+      <c r="B203" s="15"/>
+      <c r="C203" s="16"/>
+      <c r="D203" s="63"/>
+      <c r="E203" s="63"/>
+      <c r="F203" s="60"/>
+      <c r="G203" s="61"/>
+      <c r="H203" s="63"/>
+      <c r="I203" s="63"/>
+      <c r="J203" s="60"/>
+      <c r="K203" s="84"/>
+      <c r="L203" s="84"/>
+      <c r="M203" s="61"/>
+    </row>
+    <row r="204" customHeight="1" spans="2:13">
+      <c r="B204" s="15"/>
+      <c r="C204" s="16"/>
+      <c r="D204" s="63"/>
+      <c r="E204" s="63"/>
+      <c r="F204" s="60"/>
+      <c r="G204" s="61"/>
+      <c r="H204" s="63"/>
+      <c r="I204" s="63"/>
+      <c r="J204" s="60"/>
+      <c r="K204" s="84"/>
+      <c r="L204" s="84"/>
+      <c r="M204" s="61"/>
+    </row>
+    <row r="205" customHeight="1" spans="2:13">
+      <c r="B205" s="15"/>
+      <c r="C205" s="16"/>
+      <c r="D205" s="63"/>
+      <c r="E205" s="63"/>
+      <c r="F205" s="60"/>
+      <c r="G205" s="61"/>
+      <c r="H205" s="63"/>
+      <c r="I205" s="63"/>
+      <c r="J205" s="60"/>
+      <c r="K205" s="84"/>
+      <c r="L205" s="84"/>
+      <c r="M205" s="61"/>
+    </row>
+    <row r="206" customHeight="1" spans="2:13">
+      <c r="B206" s="15"/>
+      <c r="C206" s="16"/>
+      <c r="D206" s="63"/>
+      <c r="E206" s="63"/>
+      <c r="F206" s="60"/>
+      <c r="G206" s="61"/>
+      <c r="H206" s="63"/>
+      <c r="I206" s="63"/>
+      <c r="J206" s="60"/>
+      <c r="K206" s="84"/>
+      <c r="L206" s="84"/>
+      <c r="M206" s="61"/>
+    </row>
+    <row r="207" customHeight="1" spans="2:13">
+      <c r="B207" s="15"/>
+      <c r="C207" s="16"/>
+      <c r="D207" s="63"/>
+      <c r="E207" s="63"/>
+      <c r="F207" s="60"/>
+      <c r="G207" s="61"/>
+      <c r="H207" s="63"/>
+      <c r="I207" s="63"/>
+      <c r="J207" s="60"/>
+      <c r="K207" s="84"/>
+      <c r="L207" s="84"/>
+      <c r="M207" s="61"/>
+    </row>
+    <row r="208" customHeight="1" spans="2:13">
+      <c r="B208" s="15"/>
+      <c r="C208" s="16"/>
+      <c r="D208" s="63"/>
+      <c r="E208" s="63"/>
+      <c r="F208" s="60"/>
+      <c r="G208" s="61"/>
+      <c r="H208" s="63"/>
+      <c r="I208" s="63"/>
+      <c r="J208" s="60"/>
+      <c r="K208" s="84"/>
+      <c r="L208" s="84"/>
+      <c r="M208" s="61"/>
+    </row>
+    <row r="209" customHeight="1" spans="2:13">
+      <c r="B209" s="15"/>
+      <c r="C209" s="16"/>
+      <c r="D209" s="63"/>
+      <c r="E209" s="63"/>
+      <c r="F209" s="60"/>
+      <c r="G209" s="61"/>
+      <c r="H209" s="63"/>
+      <c r="I209" s="63"/>
+      <c r="J209" s="60"/>
+      <c r="K209" s="84"/>
+      <c r="L209" s="84"/>
+      <c r="M209" s="61"/>
+    </row>
   </sheetData>
-  <mergeCells count="415">
+  <mergeCells count="588">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="K2:N2"/>
@@ -5258,14 +6329,16 @@
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="O131:P131"/>
     <mergeCell ref="Q131:R131"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="F132:G132"/>
     <mergeCell ref="O132:P132"/>
     <mergeCell ref="Q132:R132"/>
-    <mergeCell ref="B133:M133"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="F133:G133"/>
     <mergeCell ref="O133:P133"/>
     <mergeCell ref="Q133:R133"/>
     <mergeCell ref="B134:C134"/>
     <mergeCell ref="F134:G134"/>
-    <mergeCell ref="J134:M134"/>
     <mergeCell ref="B135:C135"/>
     <mergeCell ref="F135:G135"/>
     <mergeCell ref="O135:S135"/>
@@ -5277,23 +6350,194 @@
     <mergeCell ref="F137:G137"/>
     <mergeCell ref="O137:P137"/>
     <mergeCell ref="Q137:R137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="F138:G138"/>
     <mergeCell ref="O138:P138"/>
     <mergeCell ref="Q138:R138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="F139:G139"/>
     <mergeCell ref="O139:P139"/>
     <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="F140:G140"/>
     <mergeCell ref="O140:P140"/>
     <mergeCell ref="Q140:R140"/>
+    <mergeCell ref="B141:C141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="F142:G142"/>
     <mergeCell ref="O142:S142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="F143:G143"/>
     <mergeCell ref="O143:P143"/>
     <mergeCell ref="Q143:R143"/>
+    <mergeCell ref="B144:C144"/>
+    <mergeCell ref="F144:G144"/>
     <mergeCell ref="O144:P144"/>
     <mergeCell ref="Q144:R144"/>
+    <mergeCell ref="B145:C145"/>
+    <mergeCell ref="F145:G145"/>
     <mergeCell ref="O145:P145"/>
     <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="B146:C146"/>
+    <mergeCell ref="F146:G146"/>
     <mergeCell ref="O146:P146"/>
     <mergeCell ref="Q146:R146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="F147:G147"/>
     <mergeCell ref="O147:P147"/>
     <mergeCell ref="Q147:R147"/>
+    <mergeCell ref="B148:C148"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="B149:C149"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="O149:S149"/>
+    <mergeCell ref="B150:C150"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="O150:P150"/>
+    <mergeCell ref="Q150:R150"/>
+    <mergeCell ref="B151:C151"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="O151:P151"/>
+    <mergeCell ref="Q151:R151"/>
+    <mergeCell ref="B152:C152"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="O152:P152"/>
+    <mergeCell ref="Q152:R152"/>
+    <mergeCell ref="B153:C153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="O153:P153"/>
+    <mergeCell ref="Q153:R153"/>
+    <mergeCell ref="B154:C154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="O154:P154"/>
+    <mergeCell ref="Q154:R154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="B156:C156"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="O156:S156"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="O157:P157"/>
+    <mergeCell ref="Q157:R157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="O158:P158"/>
+    <mergeCell ref="Q158:R158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="O159:P159"/>
+    <mergeCell ref="Q159:R159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="O160:P160"/>
+    <mergeCell ref="Q160:R160"/>
+    <mergeCell ref="B161:C161"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="O161:P161"/>
+    <mergeCell ref="Q161:R161"/>
+    <mergeCell ref="B162:C162"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="O163:S163"/>
+    <mergeCell ref="O164:P164"/>
+    <mergeCell ref="Q164:R164"/>
+    <mergeCell ref="O165:P165"/>
+    <mergeCell ref="Q165:R165"/>
+    <mergeCell ref="B166:M166"/>
+    <mergeCell ref="O166:P166"/>
+    <mergeCell ref="Q166:R166"/>
+    <mergeCell ref="B167:C167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="J167:M167"/>
+    <mergeCell ref="O167:P167"/>
+    <mergeCell ref="Q167:R167"/>
+    <mergeCell ref="B168:C168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="O168:P168"/>
+    <mergeCell ref="Q168:R168"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="B170:C170"/>
+    <mergeCell ref="F170:G170"/>
+    <mergeCell ref="B171:C171"/>
+    <mergeCell ref="F171:G171"/>
+    <mergeCell ref="B172:C172"/>
+    <mergeCell ref="F172:G172"/>
+    <mergeCell ref="B173:C173"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="B175:C175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="B176:C176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="B177:C177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="B180:C180"/>
+    <mergeCell ref="F180:G180"/>
+    <mergeCell ref="B181:C181"/>
+    <mergeCell ref="F181:G181"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="F182:G182"/>
+    <mergeCell ref="B183:C183"/>
+    <mergeCell ref="F183:G183"/>
+    <mergeCell ref="B184:C184"/>
+    <mergeCell ref="F184:G184"/>
+    <mergeCell ref="B185:C185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="B186:C186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="F188:G188"/>
+    <mergeCell ref="B189:C189"/>
+    <mergeCell ref="F189:G189"/>
+    <mergeCell ref="B190:C190"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="B191:C191"/>
+    <mergeCell ref="F191:G191"/>
+    <mergeCell ref="B192:C192"/>
+    <mergeCell ref="F192:G192"/>
+    <mergeCell ref="B193:C193"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="F194:G194"/>
+    <mergeCell ref="B195:C195"/>
+    <mergeCell ref="F195:G195"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="B197:C197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="B199:C199"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="B200:C200"/>
+    <mergeCell ref="F200:G200"/>
+    <mergeCell ref="B201:C201"/>
+    <mergeCell ref="F201:G201"/>
+    <mergeCell ref="B202:C202"/>
+    <mergeCell ref="F202:G202"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="F203:G203"/>
+    <mergeCell ref="B204:C204"/>
+    <mergeCell ref="F204:G204"/>
+    <mergeCell ref="B205:C205"/>
+    <mergeCell ref="F205:G205"/>
+    <mergeCell ref="B206:C206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="B207:C207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="B208:C208"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="B209:C209"/>
+    <mergeCell ref="F209:G209"/>
     <mergeCell ref="B36:B43"/>
     <mergeCell ref="B46:B54"/>
     <mergeCell ref="B57:B59"/>

--- a/冒险者角色档案.xlsx
+++ b/冒险者角色档案.xlsx
@@ -2131,7 +2131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:X209"/>
+  <dimension ref="B2:X230"/>
   <sheetFormatPr defaultColWidth="10.775" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.275" style="1" customWidth="1"/>
@@ -6026,6 +6026,73 @@
       <c r="K209" s="84"/>
       <c r="L209" s="84"/>
       <c r="M209" s="61"/>
+    </row>
+    <row r="210">
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>图纸（专业槽位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="O211"/>
+    </row>
+    <row r="212">
+      <c r="O212"/>
+    </row>
+    <row r="213">
+      <c r="O213"/>
+    </row>
+    <row r="214">
+      <c r="O214"/>
+    </row>
+    <row r="215">
+      <c r="O215"/>
+    </row>
+    <row r="216">
+      <c r="O216"/>
+    </row>
+    <row r="217">
+      <c r="O217"/>
+    </row>
+    <row r="218">
+      <c r="O218"/>
+    </row>
+    <row r="219">
+      <c r="O219"/>
+    </row>
+    <row r="220">
+      <c r="O220"/>
+    </row>
+    <row r="221">
+      <c r="O221"/>
+    </row>
+    <row r="222">
+      <c r="O222"/>
+    </row>
+    <row r="223">
+      <c r="O223"/>
+    </row>
+    <row r="224">
+      <c r="O224"/>
+    </row>
+    <row r="225">
+      <c r="O225"/>
+    </row>
+    <row r="226">
+      <c r="O226"/>
+    </row>
+    <row r="227">
+      <c r="O227"/>
+    </row>
+    <row r="228">
+      <c r="O228"/>
+    </row>
+    <row r="229">
+      <c r="O229"/>
+    </row>
+    <row r="230">
+      <c r="O230"/>
     </row>
   </sheetData>
   <mergeCells count="588">
